--- a/results/reliability_eval/Llama-3-8B_P176_sample_15_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P176_sample_15_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.4759493789900244</v>
+        <v>0.5510230673526346</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8698886270519708</v>
+        <v>0.881458048169077</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4759493789900244</v>
+        <v>0.5510230673526346</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8698886270519708</v>
+        <v>0.881458048169077</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5167263701238259</v>
+        <v>0.48098036248697</v>
       </c>
       <c r="F2" t="n">
-        <v>0.877397648889823</v>
+        <v>0.8820736668042473</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9992995421167931</v>
+        <v>0.9999327482430478</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998622324820071</v>
+        <v>0.9999786649598634</v>
       </c>
       <c r="I2" t="n">
-        <v>0.879</v>
+        <v>0.862</v>
       </c>
     </row>
   </sheetData>
